--- a/artfynd/A 13785-2026 artfynd.xlsx
+++ b/artfynd/A 13785-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120756592</v>
+        <v>120756591</v>
       </c>
       <c r="B2" t="n">
-        <v>58177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419576</v>
+        <v>419511</v>
       </c>
       <c r="R2" t="n">
-        <v>6405561</v>
+        <v>6405612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Jämte dike.</t>
+          <t>Jämte dike</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,15 +779,349 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Strängsered 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120756592</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NV om Strängsered, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>419576</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6405561</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gullered</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Jämte dike.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Strängsered 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120756612</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NV om Strängsered, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419516</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6405622</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gullered</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl, Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Strängsered 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120756555</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NV om Strängsered, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419605</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6405585</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gullered</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>

--- a/artfynd/A 13785-2026 artfynd.xlsx
+++ b/artfynd/A 13785-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756592</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756555</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>